--- a/doc/PRooFPS-dd-Packet-Rates.xlsx
+++ b/doc/PRooFPS-dd-Packet-Rates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__PR00F__\___developing___\projects\PRooFPS-dd\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FF5142-82DF-403E-9415-13A761965FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200449F2-45B5-4107-A6BB-55093DD222AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3B884228-A0CD-4E16-8D2B-359C9F8D4720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{3B884228-A0CD-4E16-8D2B-359C9F8D4720}"/>
   </bookViews>
   <sheets>
     <sheet name="Packet Sizes" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="111">
   <si>
     <t>v0.1.2</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>Add bDescend to UserCmdFromClient.</t>
+  </si>
+  <si>
+    <t>v0.7.1</t>
   </si>
 </sst>
 </file>
@@ -992,7 +995,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1120,6 +1123,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1141,6 +1147,51 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1183,9 +1234,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1198,48 +1246,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1258,8 +1264,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1643,26 +1653,26 @@
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="49" t="s">
         <v>81</v>
       </c>
       <c r="C10" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="48"/>
     </row>
     <row r="11" spans="1:18" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="51"/>
-      <c r="B11" s="49"/>
+      <c r="A11" s="52"/>
+      <c r="B11" s="50"/>
       <c r="C11" s="28" t="s">
         <v>15</v>
       </c>
@@ -2156,11 +2166,11 @@
         <v>71</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" ref="E26:E34" si="1">8+15</f>
+        <f t="shared" ref="E26:E35" si="1">8+15</f>
         <v>23</v>
       </c>
       <c r="F26" s="10">
-        <f t="shared" ref="F26:F34" si="2">88+15</f>
+        <f t="shared" ref="F26:F35" si="2">88+15</f>
         <v>103</v>
       </c>
       <c r="G26" s="10">
@@ -2240,11 +2250,11 @@
         <v>103</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" ref="G28:G34" si="3">68+15</f>
+        <f t="shared" ref="G28:G35" si="3">68+15</f>
         <v>83</v>
       </c>
       <c r="H28" s="44">
-        <f t="shared" ref="H28:H34" si="4">52+15</f>
+        <f t="shared" ref="H28:H35" si="4">52+15</f>
         <v>67</v>
       </c>
       <c r="I28" s="5"/>
@@ -2446,7 +2456,7 @@
       <c r="A34" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B34" s="91" t="s">
+      <c r="B34" s="45" t="s">
         <v>109</v>
       </c>
       <c r="C34" s="26">
@@ -2479,13 +2489,34 @@
       <c r="N34" s="5"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="A35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="26">
+        <v>39</v>
+      </c>
+      <c r="D35" s="33">
+        <v>91</v>
+      </c>
+      <c r="E35" s="10">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="F35" s="10">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="G35" s="10">
+        <f t="shared" si="3"/>
+        <v>83</v>
+      </c>
+      <c r="H35" s="44">
+        <f t="shared" si="4"/>
+        <v>67</v>
+      </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -2515,7 +2546,7 @@
     <mergeCell ref="A10:A11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C12:C34">
+  <conditionalFormatting sqref="C12:C35">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -2527,7 +2558,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D12:D34">
+  <conditionalFormatting sqref="D12:D35">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2539,7 +2570,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E12:E34">
+  <conditionalFormatting sqref="E12:E35">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -2551,7 +2582,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12:F34">
+  <conditionalFormatting sqref="F12:F35">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2563,7 +2594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G12:G34">
+  <conditionalFormatting sqref="G12:G35">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2575,7 +2606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H34">
+  <conditionalFormatting sqref="H12:H35">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2806,87 +2837,87 @@
     </row>
     <row r="28" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:23" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="52" t="s">
+      <c r="A29" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="60" t="s">
+      <c r="C29" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="62"/>
-      <c r="E29" s="63" t="s">
+      <c r="D29" s="78"/>
+      <c r="E29" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="63"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
-      <c r="L29" s="63"/>
-      <c r="M29" s="63"/>
-      <c r="N29" s="60" t="s">
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="O29" s="61"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="62"/>
+      <c r="O29" s="77"/>
+      <c r="P29" s="77"/>
+      <c r="Q29" s="78"/>
     </row>
     <row r="30" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="73" t="s">
+      <c r="A30" s="69"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="78" t="s">
+      <c r="D30" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="E30" s="75" t="s">
+      <c r="E30" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66" t="s">
+      <c r="F30" s="58"/>
+      <c r="G30" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="68" t="s">
+      <c r="H30" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="66" t="s">
+      <c r="I30" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="J30" s="66" t="s">
+      <c r="J30" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="K30" s="70"/>
-      <c r="L30" s="76" t="s">
+      <c r="K30" s="85"/>
+      <c r="L30" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="M30" s="77"/>
-      <c r="N30" s="64" t="s">
+      <c r="M30" s="60"/>
+      <c r="N30" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="O30" s="65"/>
-      <c r="P30" s="58" t="s">
+      <c r="O30" s="81"/>
+      <c r="P30" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="Q30" s="59"/>
+      <c r="Q30" s="75"/>
     </row>
     <row r="31" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="54"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="79"/>
+      <c r="A31" s="70"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G31" s="67"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="67"/>
+      <c r="G31" s="82"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="82"/>
       <c r="J31" s="13" t="s">
         <v>63</v>
       </c>
@@ -2927,11 +2958,11 @@
         <f>1-(C32/$C$32)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="83">
+      <c r="E32" s="66">
         <f>$C$10*$C$14</f>
         <v>480</v>
       </c>
-      <c r="F32" s="84"/>
+      <c r="F32" s="67"/>
       <c r="G32" s="7">
         <f>$C$10*$C$14</f>
         <v>480</v>
@@ -2944,11 +2975,11 @@
         <f>$C$9*$C$14</f>
         <v>420</v>
       </c>
-      <c r="J32" s="80">
+      <c r="J32" s="63">
         <f>$C$11*$C$14+$C$12</f>
         <v>2936</v>
       </c>
-      <c r="K32" s="81"/>
+      <c r="K32" s="64"/>
       <c r="L32" s="16">
         <f t="shared" ref="L32:L46" si="0">E32+G32+H32+I32+J32</f>
         <v>4383</v>
@@ -2995,11 +3026,11 @@
         <f t="shared" ref="D33:D45" si="2">1-(C33/$C$32)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="71">
+      <c r="E33" s="53">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="F33" s="72"/>
+      <c r="F33" s="54"/>
       <c r="G33" s="10">
         <f t="shared" si="1"/>
         <v>480</v>
@@ -3012,11 +3043,11 @@
         <f t="shared" ref="I33:I35" si="4">$C$9*$C$14</f>
         <v>420</v>
       </c>
-      <c r="J33" s="72">
+      <c r="J33" s="54">
         <f t="shared" ref="J33:J34" si="5">$C$11*$C$14+$C$12</f>
         <v>2936</v>
       </c>
-      <c r="K33" s="82"/>
+      <c r="K33" s="65"/>
       <c r="L33" s="17">
         <f t="shared" si="0"/>
         <v>4383</v>
@@ -3063,11 +3094,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E34" s="71">
+      <c r="E34" s="53">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="F34" s="72"/>
+      <c r="F34" s="54"/>
       <c r="G34" s="10">
         <f t="shared" si="1"/>
         <v>480</v>
@@ -3080,11 +3111,11 @@
         <f t="shared" si="4"/>
         <v>420</v>
       </c>
-      <c r="J34" s="72">
+      <c r="J34" s="54">
         <f t="shared" si="5"/>
         <v>2936</v>
       </c>
-      <c r="K34" s="82"/>
+      <c r="K34" s="65"/>
       <c r="L34" s="17">
         <f t="shared" si="0"/>
         <v>4383</v>
@@ -3131,11 +3162,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E35" s="71">
+      <c r="E35" s="53">
         <f>$C$10*$C$16</f>
         <v>160</v>
       </c>
-      <c r="F35" s="72"/>
+      <c r="F35" s="54"/>
       <c r="G35" s="10">
         <f>$C$10*$C$16</f>
         <v>160</v>
@@ -3202,11 +3233,11 @@
         <f t="shared" si="2"/>
         <v>0.73333333333333339</v>
       </c>
-      <c r="E36" s="71">
+      <c r="E36" s="53">
         <f t="shared" ref="E36" si="10">$C$10*$C$16</f>
         <v>160</v>
       </c>
-      <c r="F36" s="72"/>
+      <c r="F36" s="54"/>
       <c r="G36" s="10">
         <f>$C$10*$C$16</f>
         <v>160</v>
@@ -3266,7 +3297,7 @@
         <v>61</v>
       </c>
       <c r="C37" s="26">
-        <f t="shared" ref="C37:C54" si="11">16*$C$10</f>
+        <f t="shared" ref="C37:C55" si="11">16*$C$10</f>
         <v>128</v>
       </c>
       <c r="D37" s="35">
@@ -3278,7 +3309,7 @@
         <v>160</v>
       </c>
       <c r="F37" s="10">
-        <f t="shared" ref="F37:F54" si="12">$C$10*$C$17</f>
+        <f t="shared" ref="F37:F55" si="12">$C$10*$C$17</f>
         <v>480</v>
       </c>
       <c r="G37" s="10">
@@ -3348,7 +3379,7 @@
         <v>0.73333333333333339</v>
       </c>
       <c r="E38" s="9">
-        <f t="shared" ref="E38:E54" si="16">$C$10*$C$18</f>
+        <f t="shared" ref="E38:E55" si="16">$C$10*$C$18</f>
         <v>160</v>
       </c>
       <c r="F38" s="10">
@@ -3356,11 +3387,11 @@
         <v>480</v>
       </c>
       <c r="G38" s="10">
-        <f t="shared" ref="G38:G54" si="17">$C$10*$C$15</f>
+        <f t="shared" ref="G38:G55" si="17">$C$10*$C$15</f>
         <v>480</v>
       </c>
       <c r="H38" s="15">
-        <f t="shared" ref="H38:H54" si="18">7 + 1*$C$14</f>
+        <f t="shared" ref="H38:H55" si="18">7 + 1*$C$14</f>
         <v>67</v>
       </c>
       <c r="I38" s="10">
@@ -3734,7 +3765,7 @@
         <v>67</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" ref="I43:I54" si="19">$C$9*2 + $C$9*2</f>
+        <f t="shared" ref="I43:I55" si="19">$C$9*2 + $C$9*2</f>
         <v>28</v>
       </c>
       <c r="J43" s="10">
@@ -4404,11 +4435,11 @@
         <v>28</v>
       </c>
       <c r="J52" s="10">
-        <f>$C$21</f>
+        <f t="shared" ref="J52:K55" si="23">$C$21</f>
         <v>160</v>
       </c>
       <c r="K52" s="15">
-        <f>$C$21</f>
+        <f t="shared" si="23"/>
         <v>160</v>
       </c>
       <c r="L52" s="17">
@@ -4416,7 +4447,7 @@
         <v>895</v>
       </c>
       <c r="M52" s="11">
-        <f t="shared" ref="M52" si="23">F52+G52+H52+I52+K52</f>
+        <f t="shared" ref="M52" si="24">F52+G52+H52+I52+K52</f>
         <v>1215</v>
       </c>
       <c r="N52" s="17">
@@ -4424,15 +4455,15 @@
         <v>6265</v>
       </c>
       <c r="O52" s="11">
-        <f t="shared" ref="O52" si="24">7*M52</f>
+        <f t="shared" ref="O52" si="25">7*M52</f>
         <v>8505</v>
       </c>
       <c r="P52" s="31">
-        <f t="shared" ref="P52" si="25">1-(N52/$N$32)</f>
+        <f t="shared" ref="P52" si="26">1-(N52/$N$32)</f>
         <v>0.79580196212639742</v>
       </c>
       <c r="Q52" s="32">
-        <f t="shared" ref="Q52" si="26">1-(O52/$O$32)</f>
+        <f t="shared" ref="Q52" si="27">1-(O52/$O$32)</f>
         <v>0.7227926078028748</v>
       </c>
       <c r="R52" s="4"/>
@@ -4454,7 +4485,7 @@
         <v>128</v>
       </c>
       <c r="D53" s="35">
-        <f t="shared" ref="D53" si="27">1-(C53/$C$32)</f>
+        <f t="shared" ref="D53" si="28">1-(C53/$C$32)</f>
         <v>0.73333333333333339</v>
       </c>
       <c r="E53" s="9">
@@ -4478,35 +4509,35 @@
         <v>28</v>
       </c>
       <c r="J53" s="10">
-        <f>$C$21</f>
+        <f t="shared" si="23"/>
         <v>160</v>
       </c>
       <c r="K53" s="15">
-        <f>$C$21</f>
+        <f t="shared" si="23"/>
         <v>160</v>
       </c>
       <c r="L53" s="17">
-        <f t="shared" ref="L53" si="28">E53+G53+H53+I53+J53</f>
+        <f t="shared" ref="L53" si="29">E53+G53+H53+I53+J53</f>
         <v>895</v>
       </c>
       <c r="M53" s="11">
-        <f t="shared" ref="M53" si="29">F53+G53+H53+I53+K53</f>
+        <f t="shared" ref="M53" si="30">F53+G53+H53+I53+K53</f>
         <v>1215</v>
       </c>
       <c r="N53" s="17">
-        <f t="shared" ref="N53" si="30">7*L53</f>
+        <f t="shared" ref="N53" si="31">7*L53</f>
         <v>6265</v>
       </c>
       <c r="O53" s="11">
-        <f t="shared" ref="O53" si="31">7*M53</f>
+        <f t="shared" ref="O53" si="32">7*M53</f>
         <v>8505</v>
       </c>
       <c r="P53" s="31">
-        <f t="shared" ref="P53" si="32">1-(N53/$N$32)</f>
+        <f t="shared" ref="P53" si="33">1-(N53/$N$32)</f>
         <v>0.79580196212639742</v>
       </c>
       <c r="Q53" s="32">
-        <f t="shared" ref="Q53" si="33">1-(O53/$O$32)</f>
+        <f t="shared" ref="Q53" si="34">1-(O53/$O$32)</f>
         <v>0.7227926078028748</v>
       </c>
       <c r="R53" s="4"/>
@@ -4528,7 +4559,7 @@
         <v>128</v>
       </c>
       <c r="D54" s="35">
-        <f t="shared" ref="D54" si="34">1-(C54/$C$32)</f>
+        <f t="shared" ref="D54" si="35">1-(C54/$C$32)</f>
         <v>0.73333333333333339</v>
       </c>
       <c r="E54" s="9">
@@ -4552,35 +4583,35 @@
         <v>28</v>
       </c>
       <c r="J54" s="10">
-        <f>$C$21</f>
+        <f t="shared" si="23"/>
         <v>160</v>
       </c>
       <c r="K54" s="15">
-        <f>$C$21</f>
+        <f t="shared" si="23"/>
         <v>160</v>
       </c>
       <c r="L54" s="17">
-        <f t="shared" ref="L54" si="35">E54+G54+H54+I54+J54</f>
+        <f t="shared" ref="L54" si="36">E54+G54+H54+I54+J54</f>
         <v>895</v>
       </c>
       <c r="M54" s="11">
-        <f t="shared" ref="M54" si="36">F54+G54+H54+I54+K54</f>
+        <f t="shared" ref="M54" si="37">F54+G54+H54+I54+K54</f>
         <v>1215</v>
       </c>
       <c r="N54" s="17">
-        <f t="shared" ref="N54" si="37">7*L54</f>
+        <f t="shared" ref="N54" si="38">7*L54</f>
         <v>6265</v>
       </c>
       <c r="O54" s="11">
-        <f t="shared" ref="O54" si="38">7*M54</f>
+        <f t="shared" ref="O54" si="39">7*M54</f>
         <v>8505</v>
       </c>
       <c r="P54" s="31">
-        <f t="shared" ref="P54" si="39">1-(N54/$N$32)</f>
+        <f t="shared" ref="P54" si="40">1-(N54/$N$32)</f>
         <v>0.79580196212639742</v>
       </c>
       <c r="Q54" s="32">
-        <f t="shared" ref="Q54" si="40">1-(O54/$O$32)</f>
+        <f t="shared" ref="Q54" si="41">1-(O54/$O$32)</f>
         <v>0.7227926078028748</v>
       </c>
       <c r="R54" s="4"/>
@@ -4590,23 +4621,73 @@
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A55" s="5"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
+    <row r="55" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="93" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" s="26">
+        <f t="shared" si="11"/>
+        <v>128</v>
+      </c>
+      <c r="D55" s="35">
+        <f t="shared" ref="D55" si="42">1-(C55/$C$32)</f>
+        <v>0.73333333333333339</v>
+      </c>
+      <c r="E55" s="9">
+        <f t="shared" si="16"/>
+        <v>160</v>
+      </c>
+      <c r="F55" s="10">
+        <f t="shared" si="12"/>
+        <v>480</v>
+      </c>
+      <c r="G55" s="10">
+        <f t="shared" si="17"/>
+        <v>480</v>
+      </c>
+      <c r="H55" s="15">
+        <f t="shared" si="18"/>
+        <v>67</v>
+      </c>
+      <c r="I55" s="10">
+        <f t="shared" si="19"/>
+        <v>28</v>
+      </c>
+      <c r="J55" s="10">
+        <f t="shared" si="23"/>
+        <v>160</v>
+      </c>
+      <c r="K55" s="15">
+        <f t="shared" si="23"/>
+        <v>160</v>
+      </c>
+      <c r="L55" s="17">
+        <f t="shared" ref="L55" si="43">E55+G55+H55+I55+J55</f>
+        <v>895</v>
+      </c>
+      <c r="M55" s="11">
+        <f t="shared" ref="M55" si="44">F55+G55+H55+I55+K55</f>
+        <v>1215</v>
+      </c>
+      <c r="N55" s="17">
+        <f t="shared" ref="N55" si="45">7*L55</f>
+        <v>6265</v>
+      </c>
+      <c r="O55" s="11">
+        <f t="shared" ref="O55" si="46">7*M55</f>
+        <v>8505</v>
+      </c>
+      <c r="P55" s="31">
+        <f t="shared" ref="P55" si="47">1-(N55/$N$32)</f>
+        <v>0.79580196212639742</v>
+      </c>
+      <c r="Q55" s="32">
+        <f t="shared" ref="Q55" si="48">1-(O55/$O$32)</f>
+        <v>0.7227926078028748</v>
+      </c>
       <c r="R55" s="4"/>
       <c r="S55" s="4"/>
       <c r="T55" s="4"/>
@@ -4649,6 +4730,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="N29:Q29"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="C30:C31"/>
@@ -4661,20 +4753,9 @@
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E34:F34"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="N29:Q29"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="C29:D29"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C32:D54">
+  <conditionalFormatting sqref="C32:D55">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -4686,7 +4767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32:D54">
+  <conditionalFormatting sqref="D32:D55">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4698,7 +4779,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E32:F54">
+  <conditionalFormatting sqref="E32:F55">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -4710,7 +4791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G32:G54">
+  <conditionalFormatting sqref="G32:G55">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -4722,7 +4803,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H32:H54">
+  <conditionalFormatting sqref="H32:H55">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -4734,7 +4815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32:I54">
+  <conditionalFormatting sqref="I32:I55">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4746,7 +4827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J32:K54">
+  <conditionalFormatting sqref="J32:K55">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -4758,7 +4839,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L32:M54">
+  <conditionalFormatting sqref="L32:M55">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -4770,7 +4851,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N32:O54">
+  <conditionalFormatting sqref="N32:O55">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4782,7 +4863,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P32:Q54">
+  <conditionalFormatting sqref="P32:Q55">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -4801,7 +4882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A631036-56BD-4CE5-917C-895C0C771D72}">
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
@@ -4867,87 +4948,87 @@
     </row>
     <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:17" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="63" t="s">
+      <c r="D15" s="78"/>
+      <c r="E15" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="60" t="s">
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="61"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="78"/>
     </row>
     <row r="16" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="53"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="73" t="s">
+      <c r="A16" s="69"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="78" t="s">
+      <c r="D16" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66" t="s">
+      <c r="F16" s="58"/>
+      <c r="G16" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="68" t="s">
+      <c r="H16" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="66" t="s">
+      <c r="I16" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="66" t="s">
+      <c r="J16" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="70"/>
-      <c r="L16" s="76" t="s">
+      <c r="K16" s="85"/>
+      <c r="L16" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="M16" s="77"/>
-      <c r="N16" s="64" t="s">
+      <c r="M16" s="60"/>
+      <c r="N16" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="O16" s="65"/>
-      <c r="P16" s="58" t="s">
+      <c r="O16" s="81"/>
+      <c r="P16" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="Q16" s="59"/>
+      <c r="Q16" s="75"/>
     </row>
     <row r="17" spans="1:17" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
-      <c r="B17" s="57"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="79"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="67"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="67"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="82"/>
       <c r="J17" s="13" t="s">
         <v>63</v>
       </c>
@@ -4988,11 +5069,11 @@
         <f>1-(C18/$C$18)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="85">
+      <c r="E18" s="86">
         <f>'Packet Rates'!E32*'Packet Sizes'!D12</f>
         <v>128640</v>
       </c>
-      <c r="F18" s="86"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="7">
         <f>'Packet Rates'!G32*'Packet Sizes'!E12</f>
         <v>128640</v>
@@ -5005,11 +5086,11 @@
         <f>'Packet Rates'!I32*'Packet Sizes'!G12</f>
         <v>112560</v>
       </c>
-      <c r="J18" s="84">
+      <c r="J18" s="67">
         <f>'Packet Rates'!J32*'Packet Sizes'!H12</f>
         <v>786848</v>
       </c>
-      <c r="K18" s="87"/>
+      <c r="K18" s="88"/>
       <c r="L18" s="16">
         <f>E18+G18+H18+I18+J18</f>
         <v>1174644</v>
@@ -5050,11 +5131,11 @@
         <f t="shared" ref="D19:D33" si="0">1-(C19/$C$18)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="88">
+      <c r="E19" s="89">
         <f>'Packet Rates'!E33*'Packet Sizes'!D13</f>
         <v>128640</v>
       </c>
-      <c r="F19" s="89"/>
+      <c r="F19" s="90"/>
       <c r="G19" s="10">
         <f>'Packet Rates'!G33*'Packet Sizes'!E13</f>
         <v>128640</v>
@@ -5067,11 +5148,11 @@
         <f>'Packet Rates'!I33*'Packet Sizes'!G13</f>
         <v>112560</v>
       </c>
-      <c r="J19" s="72">
+      <c r="J19" s="54">
         <f>'Packet Rates'!J33*'Packet Sizes'!H13</f>
         <v>786848</v>
       </c>
-      <c r="K19" s="90"/>
+      <c r="K19" s="91"/>
       <c r="L19" s="17">
         <f t="shared" ref="L19:L33" si="1">E19+G19+H19+I19+J19</f>
         <v>1174644</v>
@@ -5112,11 +5193,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="88">
+      <c r="E20" s="89">
         <f>'Packet Rates'!E34*'Packet Sizes'!D14</f>
         <v>128640</v>
       </c>
-      <c r="F20" s="89"/>
+      <c r="F20" s="90"/>
       <c r="G20" s="10">
         <f>'Packet Rates'!G34*'Packet Sizes'!E14</f>
         <v>128640</v>
@@ -5129,11 +5210,11 @@
         <f>'Packet Rates'!I34*'Packet Sizes'!G14</f>
         <v>112560</v>
       </c>
-      <c r="J20" s="72">
+      <c r="J20" s="54">
         <f>'Packet Rates'!J34*'Packet Sizes'!H14</f>
         <v>786848</v>
       </c>
-      <c r="K20" s="90"/>
+      <c r="K20" s="91"/>
       <c r="L20" s="17">
         <f t="shared" si="1"/>
         <v>1174644</v>
@@ -5174,11 +5255,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="71">
+      <c r="E21" s="53">
         <f>'Packet Rates'!E35*'Packet Sizes'!D15</f>
         <v>42880</v>
       </c>
-      <c r="F21" s="72"/>
+      <c r="F21" s="54"/>
       <c r="G21" s="10">
         <f>'Packet Rates'!G35*'Packet Sizes'!E15</f>
         <v>42880</v>
@@ -5239,11 +5320,11 @@
         <f t="shared" si="0"/>
         <v>0.96915422885572144</v>
       </c>
-      <c r="E22" s="71">
+      <c r="E22" s="53">
         <f>'Packet Rates'!E36*'Packet Sizes'!D16</f>
         <v>8800</v>
       </c>
-      <c r="F22" s="72"/>
+      <c r="F22" s="54"/>
       <c r="G22" s="10">
         <f>'Packet Rates'!G36*'Packet Sizes'!E16</f>
         <v>3680</v>
@@ -6513,8 +6594,85 @@
         <v>0.93643606062773066</v>
       </c>
     </row>
+    <row r="41" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="93" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="26">
+        <f>'Packet Rates'!C55*'Packet Sizes'!C35</f>
+        <v>4992</v>
+      </c>
+      <c r="D41" s="37">
+        <f t="shared" ref="D41" si="36">1-(C41/$C$18)</f>
+        <v>0.96119402985074631</v>
+      </c>
+      <c r="E41" s="9">
+        <f>'Packet Rates'!E55*'Packet Sizes'!D35</f>
+        <v>14560</v>
+      </c>
+      <c r="F41" s="10">
+        <f>'Packet Rates'!F55*'Packet Sizes'!D35</f>
+        <v>43680</v>
+      </c>
+      <c r="G41" s="10">
+        <f>'Packet Rates'!G55*'Packet Sizes'!E35</f>
+        <v>11040</v>
+      </c>
+      <c r="H41" s="10">
+        <f>'Packet Rates'!H55*'Packet Sizes'!F35</f>
+        <v>6901</v>
+      </c>
+      <c r="I41" s="10">
+        <f>'Packet Rates'!I55*'Packet Sizes'!G35</f>
+        <v>2324</v>
+      </c>
+      <c r="J41" s="10">
+        <f>'Packet Rates'!J55*'Packet Sizes'!H35</f>
+        <v>10720</v>
+      </c>
+      <c r="K41" s="15">
+        <f>'Packet Rates'!K55*'Packet Sizes'!H35</f>
+        <v>10720</v>
+      </c>
+      <c r="L41" s="17">
+        <f t="shared" ref="L41" si="37">E41+G41+H41+I41+J41</f>
+        <v>45545</v>
+      </c>
+      <c r="M41" s="11">
+        <f t="shared" ref="M41" si="38">F41+G41+H41+I41+K41</f>
+        <v>74665</v>
+      </c>
+      <c r="N41" s="17">
+        <f t="shared" ref="N41" si="39">L41*7</f>
+        <v>318815</v>
+      </c>
+      <c r="O41" s="11">
+        <f t="shared" ref="O41" si="40">M41*7</f>
+        <v>522655</v>
+      </c>
+      <c r="P41" s="31">
+        <f t="shared" ref="P41" si="41">1-(N41/$N$18)</f>
+        <v>0.96122655034206106</v>
+      </c>
+      <c r="Q41" s="32">
+        <f t="shared" ref="Q41" si="42">1-(O41/$O$18)</f>
+        <v>0.93643606062773066</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="J20:K20"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="E15:M15"/>
@@ -6529,18 +6687,9 @@
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="J20:K20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C18:D40">
+  <conditionalFormatting sqref="C18:D41">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -6552,7 +6701,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D40">
+  <conditionalFormatting sqref="D18:D41">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -6564,7 +6713,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E18:E20 E21:F40">
+  <conditionalFormatting sqref="E18:E20 E21:F41">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -6576,7 +6725,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G18:G40">
+  <conditionalFormatting sqref="G18:G41">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -6588,7 +6737,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H40">
+  <conditionalFormatting sqref="H18:H41">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -6600,7 +6749,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18:I40">
+  <conditionalFormatting sqref="I18:I41">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -6612,7 +6761,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J18:K40">
+  <conditionalFormatting sqref="J18:K41">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -6624,7 +6773,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L18:M40">
+  <conditionalFormatting sqref="L18:M41">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -6636,7 +6785,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N18:P40">
+  <conditionalFormatting sqref="N18:P41">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -6648,7 +6797,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P18:P40">
+  <conditionalFormatting sqref="P18:P41">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -6710,7 +6859,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q18:Q40">
+  <conditionalFormatting sqref="Q18:Q41">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
